--- a/object_repo/dgx_demo_object_repository_cn.xlsx
+++ b/object_repo/dgx_demo_object_repository_cn.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -782,6 +782,171 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DGXManagePage</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DGX Design</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>dom_ready</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DGX exercise 管理页</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>dgx</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>用于创建新的 DGX exercise。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>/dgx/*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DGX Design</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dom_ready</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>录制生成 exercise 的 Site Conf 页面</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>dgx</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>用于 plot 选择、Set Boundaries 和 Site Conf 数值输入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>/dgx/*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DGX Design</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dom_ready</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>录制生成 exercise 的 Surrounding Conf 页面</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dgx</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>用于 Buildings、POI、Roads 和 Land Cover 相关操作。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="anysvml"/>
@@ -794,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2119,6 +2284,2946 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>create_exercise_button</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Create exercise 按钮</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DGXManagePage</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Create New DGX Exercise</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>.create-exercise-btn</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ExerciseCreate.Trigger</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Opens the create exercise dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>exercise_name_input</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>exercise 名称输入框</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DGXManagePage</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>div[id^='headlessui-dialog-panel'] input.w-full.h-14</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>//div[contains(@id,'headlessui-dialog-panel')]//input[@type='text']</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ExerciseCreate.NameInput</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Inputs the new exercise name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>create_exercise_submit_button</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>创建弹窗提交按钮</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DGXManagePage</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>//div[contains(@id,'headlessui-dialog-panel')]//button[normalize-space()='Create']</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>div[id^='headlessui-dialog-panel'] button.h-12.px-10</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>ExerciseCreate.Submit</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Submits the create exercise dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>exercise_title_heading</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>exercise 标题</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>//header//h1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>header h1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Exercise.HeaderTitle</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Shows the current exercise name in the page header.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>plot_marker_button</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>plot 标记点</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>div.leaflet-marker-icon.custom-div-icon[role='button']</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>(//*[@role='button' and contains(@class,'custom-div-icon')])[1]</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PlotSelection.Marker</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Opens the plot popover on the map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>plot_go_to_configuration_button</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>plot 的 Go to Configuration 按钮</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Go to Configuration</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Go to Configuration</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>PlotSelection.GoToConfiguration</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Enters the selected plot configuration flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>layer_select_button_3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>第 3 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[3]</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect3</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Third selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>layer_select_button_4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>第 4 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[4]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect4</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Fourth selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>layer_select_button_5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>第 5 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[5]</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect5</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Fifth selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>layer_select_button_6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>第 6 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[6]</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect6</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Sixth selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>layer_select_button_7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>第 7 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[7]</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect7</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Seventh selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>layer_select_button_8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>第 8 个图层选择器</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(//button[contains(normalize-space(.), '---- Select a Layer ----')])[8]</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>BoundaryModal.LayerSelect8</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Eighth selector in the boundary layer modal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>boundary_modal_save_button</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>边界弹窗保存按钮</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>//div[contains(@class,'lc-content')]//button[normalize-space()='Save']</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>BoundaryModal.Save</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Saves the current boundary layer choices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>plot_assignment_input_1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>第一个数值输入框</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>div.row &gt; div.cell.value &gt; div.custom-input-number.w-full &gt; input</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>(//div[contains(@class,'custom-input-number')]//input)[1]</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>SiteConf.NumericInput1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>The first numeric field that was filled with 35 in the recording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>plot_assignment_input_2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>第二个数值输入框</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DGXRecordedSiteConfPage</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>div.mt-4 &gt; div.my-6 &gt; div.custom-input-number.w-full &gt; input</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>(//div[contains(@class,'custom-input-number')]//input)[2]</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>SiteConf.NumericInput2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>The second numeric field that was filled with 1 in the recording.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>surrounding_next_button</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Surrounding 下一步按钮</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-footer-next') and normalize-space()='Next']</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>button.sc-footer-btn.sc-footer-next</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SurroundingFlow.Next</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Moves between Buildings, POI, Roads and Land Cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>surrounding_done_button</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Surrounding 完成按钮</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-footer-next') and normalize-space()='Done']</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>button.sc-footer-btn.sc-footer-next</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>SurroundingFlow.Done</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Final button on the last Surrounding Conf step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>surrounding_building_row_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>第一条 Buildings 表格记录</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Building 01</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>table.dgx-table tbody tr td.sc-col-name</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SurroundingBuildings.Row1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Opens the first building detail popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>building_detail_close_button</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>building 详情关闭按钮</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>button.sc-building-detail-close</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-building-detail-close')]</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>SurroundingBuildings.DetailClose</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Closes the building detail popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>add_custom_poi_button</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Add Custom POI 按钮</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Add Custom POI</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>button.sc-add-btn</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.Add</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Opens the custom POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>poi_name_input</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>POI 名称输入框</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>input[placeholder*='POI Name']</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'POI Name')]</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.NameInput</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Name input inside the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>poi_type_input</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>POI 类型输入框</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>input[placeholder*='POI Type']</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'POI Type')]</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.TypeInput</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Type input inside the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>poi_latitude_input</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>POI 纬度输入框</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>input[placeholder*='Latitude']</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'Latitude')]</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.LatitudeInput</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Latitude input inside the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>poi_longitude_input</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>POI 经度输入框</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>input[placeholder*='Longitude']</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'Longitude')]</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>10</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.LongitudeInput</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Longitude input inside the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>poi_select_local_file_button</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>POI 选择本地文件按钮</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Select local file</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Select local file']</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.SelectLocalFile</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Opens the local file chooser in the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>poi_file_input</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>POI 文件输入框</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>input.sc-poi-file-input</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>//input[contains(@class,'sc-poi-file-input')]</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.FileInput</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Hidden file input used by the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>poi_cancel_button</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>POI 表单取消按钮</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>button.sc-poi-action.sc-poi-cancel</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-poi-cancel') and normalize-space()='Cancel']</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>10</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.Cancel</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Closes the POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>poi_save_button</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>POI 表单保存按钮</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>button.sc-poi-action.sc-poi-save</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-poi-save') and normalize-space()='Save']</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>10</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.Save</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Saves the custom POI form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>poi_delete_button</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>POI 删除按钮</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>button.sc-poi-delete-btn</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-poi-delete-btn')]</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>SurroundingPOI.Delete</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Deletes the selected custom POI row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>add_custom_land_cover_button</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Add Custom Land Cover 按钮</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Add Custom Land Cover</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>button.sc-add-btn</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>10</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Add</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Opens the custom Land Cover form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>land_cover_name_input</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Land Cover 名称输入框</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>input[placeholder*='Land Cover Name']</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'Land Cover Name')]</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.NameInput</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Name input inside the Land Cover form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>land_cover_type_select</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Land Cover 类型下拉框</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>div.sc-poi-form-wrap select</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>//div[contains(@class,'sc-poi-form-wrap')]//select</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>10</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.TypeSelect</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Type select inside the Land Cover form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>land_cover_map_canvas</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Land Cover 绘制地图</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>div.sc-poi-map-wrap div.leaflet-container.leaflet-touch</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>//div[contains(@class,'sc-poi-map-wrap')]//div[contains(@class,'leaflet-container')]</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>10</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Map</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Map container used for Land Cover drawing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>land_cover_start_draw_button</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Land Cover Start Draw 按钮</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Start Draw</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Start Draw']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>10</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.StartDraw</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Enters the draw mode of the Land Cover form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>land_cover_undo_button</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Land Cover Undo 按钮</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Undo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Undo']</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Undo</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Undoes the last Land Cover point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>land_cover_delete_button</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Land Cover Delete 按钮</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Delete']</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>10</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Delete</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Deletes the current Land Cover drawing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>land_cover_complete_button</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Land Cover Complete 按钮</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Complete']</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Complete</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Completes the Land Cover drawing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>land_cover_edit_button</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Land Cover Edit 按钮</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>partial_text</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>//button[normalize-space()='Edit']</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Edit</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Edits the completed Land Cover drawing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>land_cover_cancel_button</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Land Cover 取消按钮</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>button.sc-poi-action.sc-poi-cancel</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-poi-cancel') and normalize-space()='Cancel']</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Cancel</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Closes the Land Cover form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>land_cover_save_button</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Land Cover 保存按钮</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DGXRecordedSurroundingPage</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>css</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>button.sc-poi-action.sc-poi-save</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>xpath</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>//button[contains(@class,'sc-poi-save') and normalize-space()='Save']</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>10</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>SurroundingLandCover.Save</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Saves the Land Cover form.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="anysvml"/>
